--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.15557970882491</v>
+        <v>2.950281702684049</v>
       </c>
       <c r="D2" t="n">
-        <v>19.11918267437521</v>
+        <v>3.106867184585973</v>
       </c>
       <c r="E2" t="n">
-        <v>8.412231604687701</v>
+        <v>1.366987635761751</v>
       </c>
       <c r="F2" t="n">
-        <v>6.897099782500063</v>
+        <v>1.12077871465626</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.0539288148033</v>
+        <v>1.958763432405536</v>
       </c>
       <c r="D3" t="n">
-        <v>13.18809546545635</v>
+        <v>2.143065513136657</v>
       </c>
       <c r="E3" t="n">
-        <v>8.412231604687701</v>
+        <v>1.366987635761751</v>
       </c>
       <c r="F3" t="n">
-        <v>6.897099782500063</v>
+        <v>1.12077871465626</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.19570362556668</v>
+        <v>2.794301839154585</v>
       </c>
       <c r="D4" t="n">
-        <v>5.321521615615247</v>
+        <v>0.8647472625374776</v>
       </c>
       <c r="E4" t="n">
-        <v>8.412231604687701</v>
+        <v>1.366987635761751</v>
       </c>
       <c r="F4" t="n">
-        <v>6.897099782500063</v>
+        <v>1.12077871465626</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.64361790324012</v>
+        <v>3.51708790927652</v>
       </c>
       <c r="D5" t="n">
-        <v>22.03532681642491</v>
+        <v>3.580740607669048</v>
       </c>
       <c r="E5" t="n">
-        <v>8.412231604687701</v>
+        <v>1.366987635761751</v>
       </c>
       <c r="F5" t="n">
-        <v>6.897099782500063</v>
+        <v>1.12077871465626</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.10646655309553</v>
+        <v>4.892300814878023</v>
       </c>
       <c r="D6" t="n">
-        <v>15.18222645068898</v>
+        <v>2.467111798236959</v>
       </c>
       <c r="E6" t="n">
-        <v>8.412231604687701</v>
+        <v>1.366987635761751</v>
       </c>
       <c r="F6" t="n">
-        <v>6.897099782500063</v>
+        <v>1.12077871465626</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>2.667549521185685</v>
+        <v>0.4334767971926738</v>
       </c>
       <c r="D7" t="n">
-        <v>2.871072577042307</v>
+        <v>0.4665492937693749</v>
       </c>
       <c r="E7" t="n">
-        <v>8.412231604687701</v>
+        <v>1.366987635761751</v>
       </c>
       <c r="F7" t="n">
-        <v>6.897099782500063</v>
+        <v>1.12077871465626</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
